--- a/excel/Revolut Brokerage Rima.xlsx
+++ b/excel/Revolut Brokerage Rima.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/69be8bcaca992739/Dokumentai/portfolio-analytics/portfolio-dashboard-clean/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Revolut\Brokerage Account Rima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{C1EE1FC9-214D-466E-AEDD-AC0AB94F2565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{423C2149-F0E0-425C-A1BC-50329235457A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E59FCE-1FFB-4DCA-808D-C908F70FBA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,14 +22,15 @@
     <sheet name="XDWT" sheetId="86" state="hidden" r:id="rId7"/>
     <sheet name="XAIX" sheetId="87" state="hidden" r:id="rId8"/>
     <sheet name="WEBN" sheetId="90" r:id="rId9"/>
-    <sheet name="2026.08" sheetId="103" r:id="rId10"/>
-    <sheet name="2026.07" sheetId="102" r:id="rId11"/>
-    <sheet name="2026.06" sheetId="101" r:id="rId12"/>
-    <sheet name="2026.05" sheetId="100" r:id="rId13"/>
-    <sheet name="2026.04" sheetId="99" r:id="rId14"/>
-    <sheet name="2026.03" sheetId="98" r:id="rId15"/>
-    <sheet name="2026.02" sheetId="97" r:id="rId16"/>
-    <sheet name="2026.01" sheetId="69" r:id="rId17"/>
+    <sheet name="2026.09" sheetId="104" r:id="rId10"/>
+    <sheet name="2026.08" sheetId="103" r:id="rId11"/>
+    <sheet name="2026.07" sheetId="102" r:id="rId12"/>
+    <sheet name="2026.06" sheetId="101" r:id="rId13"/>
+    <sheet name="2026.05" sheetId="100" r:id="rId14"/>
+    <sheet name="2026.04" sheetId="99" r:id="rId15"/>
+    <sheet name="2026.03" sheetId="98" r:id="rId16"/>
+    <sheet name="2026.02" sheetId="97" r:id="rId17"/>
+    <sheet name="2026.01" sheetId="69" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="48">
   <si>
     <t>Kaina</t>
   </si>
@@ -452,7 +453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -551,9 +552,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -575,24 +573,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -691,6 +671,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -765,7 +748,119 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8CD4EA-FC4D-4D0C-BD92-E92FEFA185E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16621125" y="190500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20A27B87-8B8C-4C4E-89F6-DA710DB39AAC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16621125" y="190500"/>
+          <a:ext cx="914400" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -821,7 +916,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -877,7 +972,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -933,7 +1028,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -989,7 +1084,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1045,7 +1140,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1101,7 +1196,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1123,62 +1218,6 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{32E77520-06CC-410E-98DF-D7780C3359DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
-          <a:extLst>
-            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId3"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="16621125" y="190500"/>
-          <a:ext cx="914400" cy="914400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Graphic 1" descr="Arrow: Rotate left with solid fill">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF8CD4EA-FC4D-4D0C-BD92-E92FEFA185E5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1476,39 +1515,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:AS17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
     <col min="2" max="13" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A1" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="59" t="s">
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="64" t="s">
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="K1" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="63"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="65"/>
+      <c r="L1" s="56"/>
+      <c r="AS1" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A2" s="58"/>
       <c r="B2" s="23" t="s">
         <v>10</v>
       </c>
@@ -1534,15 +1576,19 @@
       <c r="I2" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="65"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="AS2" s="21">
+        <f ca="1">XIRR(WEBN!AG5:AG200,WEBN!AF5:AF200)</f>
+        <v>0.23258460164070127</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="36">
         <f>'2026.01'!Q2</f>
         <v>2026.01</v>
@@ -1592,7 +1638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="36">
         <f>'2026.02'!Q2</f>
         <v>2026.02</v>
@@ -1642,7 +1688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <f>'2026.03'!Q2</f>
         <v>2026.03</v>
@@ -1692,7 +1738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <f>'2026.04'!$Q$2</f>
         <v>2026.04</v>
@@ -1742,7 +1788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="36">
         <f>'2026.05'!$Q$2</f>
         <v>2026.05</v>
@@ -1792,7 +1838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <f>'2026.06'!$Q$2</f>
         <v>2026.06</v>
@@ -1842,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
         <f>'2026.07'!$Q$2</f>
         <v>2026.07</v>
@@ -1892,7 +1938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <f>'2026.08'!$Q$2</f>
         <v>2026.08</v>
@@ -1942,21 +1988,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="21"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="A11" s="36">
+        <f>'2026.09'!$Q$2</f>
+        <v>2026.09</v>
+      </c>
+      <c r="B11" s="4">
+        <f>B10+'2026.09'!$Q$5</f>
+        <v>900</v>
+      </c>
+      <c r="C11" s="4">
+        <f>'2026.09'!$R$5</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="4">
+        <f>D10+'2026.09'!$S$5-K11-L11</f>
+        <v>900</v>
+      </c>
+      <c r="E11" s="4">
+        <f>'2026.09'!$X$5</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="4">
+        <f>WEBN!H13</f>
+        <v>974.40370280651996</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" ref="G11" si="9">SUM(F11:F11)+E11</f>
+        <v>974.40370280651996</v>
+      </c>
+      <c r="H11" s="4">
+        <f t="shared" ref="H11" si="10">G11-B11</f>
+        <v>74.403702806519959</v>
+      </c>
+      <c r="I11" s="21">
+        <f t="shared" ref="I11" si="11">H11/B11</f>
+        <v>8.2670780896133292E-2</v>
+      </c>
+      <c r="J11" s="4">
+        <f>'2026.09'!$W$5</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="4">
+        <f>'2026.09'!$U$5</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="4">
+        <f>'2026.09'!$V$5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1970,7 +2052,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -1984,7 +2066,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1998,7 +2080,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2012,7 +2094,7 @@
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -2057,7 +2139,8 @@
     <hyperlink ref="F2" location="WEBN!A1" display="WEBN!A1" xr:uid="{499756ED-B1F9-4D05-897B-F69DF5557EF9}"/>
     <hyperlink ref="A8" location="'2026.06'!A1" display="'2026.06'!A1" xr:uid="{EDD493B5-6E5A-4B6F-9C2F-600CF21AFF32}"/>
     <hyperlink ref="A9" location="'2026.07'!A1" display="'2026.07'!A1" xr:uid="{0EA64D34-DE59-4B69-AFFB-31BBE94C6E84}"/>
-    <hyperlink ref="A10" location="'2026.08'!A1" display="'2026.08'!A1" xr:uid="{EBA7FF03-B603-4FA0-A3D1-936DE1CCCC75}"/>
+    <hyperlink ref="A10" location="'2026.08'!A1" display="'2026.08'!A1" xr:uid="{C639A19F-ADDC-466B-866D-98C0CF46D416}"/>
+    <hyperlink ref="A11" location="'2026.09'!A1" display="'2026.09'!A1" xr:uid="{266A05DA-DB58-4AB4-988A-01080B59A77E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2065,7 +2148,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994F0C49-1D2F-4997-8556-A5B08EA369F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBDDE6DF-DFE1-49B3-A2B6-A2C307187AC4}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2081,54 +2164,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
-        <v>2026.08</v>
-      </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="Q2" s="73">
+        <v>2026.09</v>
+      </c>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -2163,95 +2246,95 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="57" t="s">
+      <c r="A14" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="56" t="s">
+      <c r="B14" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="56" t="s">
+      <c r="C14" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="D14" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="F14" s="56" t="s">
+      <c r="E14" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="56" t="s">
+      <c r="G14" s="69"/>
+      <c r="H14" s="49" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="56" t="s">
+      <c r="I14" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="56" t="s">
+      <c r="J14" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="K14" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="L14" s="54" t="s">
+      <c r="K14" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="L14" s="47" t="s">
         <v>1</v>
       </c>
       <c r="M14" s="31"/>
-      <c r="N14" s="55" t="s">
+      <c r="N14" s="48" t="s">
         <v>32</v>
       </c>
-      <c r="O14" s="56" t="s">
+      <c r="O14" s="49" t="s">
         <v>29</v>
       </c>
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
-        <v>46252</v>
+      <c r="A15" s="40">
+        <v>46275</v>
       </c>
       <c r="B15" s="11">
         <v>100</v>
@@ -2264,30 +2347,30 @@
       </c>
       <c r="E15" s="11">
         <f>C15/F15</f>
-        <v>12.900000007481999</v>
+        <v>12.820000004076761</v>
       </c>
       <c r="F15" s="13">
-        <v>7.7519379800000001</v>
-      </c>
-      <c r="G15" s="76"/>
+        <v>7.8003120099999999</v>
+      </c>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="24"/>
-      <c r="M15" s="58"/>
+      <c r="M15" s="51"/>
       <c r="N15" s="25"/>
       <c r="O15" s="4"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2298,13 +2381,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2315,13 +2398,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2332,7 +2415,7 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="49" t="s">
         <v>2</v>
       </c>
       <c r="B19" s="4">
@@ -2349,14 +2432,14 @@
       </c>
       <c r="E19" s="4">
         <f>IF(B19&gt;0,SUMPRODUCT(E15:E18,F15:F18)/SUM(F15:F18),"0.00")</f>
-        <v>12.900000007481999</v>
+        <v>12.820000004076761</v>
       </c>
       <c r="F19" s="13">
         <f>SUM(F15:F18)</f>
-        <v>7.7519379800000001</v>
-      </c>
-      <c r="G19" s="77"/>
-      <c r="H19" s="56" t="s">
+        <v>7.8003120099999999</v>
+      </c>
+      <c r="G19" s="70"/>
+      <c r="H19" s="49" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="4">
@@ -2373,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="33"/>
-      <c r="N19" s="56" t="s">
+      <c r="N19" s="49" t="s">
         <v>2</v>
       </c>
       <c r="O19" s="4">
@@ -2415,6 +2498,368 @@
     <mergeCell ref="N13:O13"/>
   </mergeCells>
   <hyperlinks>
+    <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{C0EE0919-08E9-4673-80F9-057FCDF56DCE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="E19" formula="1"/>
+  </ignoredErrors>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{994F0C49-1D2F-4997-8556-A5B08EA369F6}">
+  <dimension ref="A2:X27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.7109375" customWidth="1"/>
+    <col min="7" max="7" width="2.7109375" customWidth="1"/>
+    <col min="8" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="2.7109375" customWidth="1"/>
+    <col min="14" max="15" width="10.7109375" customWidth="1"/>
+    <col min="16" max="16" width="5.7109375" customWidth="1"/>
+    <col min="17" max="24" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q2" s="73">
+        <v>2026.08</v>
+      </c>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q3" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="R3" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="S3" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="T3" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="U3" s="77" t="s">
+        <v>30</v>
+      </c>
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" s="61" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Q5" s="4">
+        <v>100</v>
+      </c>
+      <c r="R5" s="4">
+        <v>0</v>
+      </c>
+      <c r="S5" s="4">
+        <f>(C19+C29+C39+C49+C59+C69+C79+C89+C99+C109)</f>
+        <v>100</v>
+      </c>
+      <c r="T5" s="4">
+        <f>(I19+I29+I39+I49+I59+I69+I79+I89+I99+I109)-V5</f>
+        <v>0</v>
+      </c>
+      <c r="U5" s="4">
+        <f>D19+D29+D39+D49+D59+D69+D79+D89+D99+D109</f>
+        <v>0</v>
+      </c>
+      <c r="V5" s="4">
+        <f>J19+J29+J39+J49+J59+J69+J79+J89+J99+J109</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="4">
+        <f>O19+O29+O39+O49+O59+O69+O79+O89+O99+O109</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="4">
+        <f>Q5-S5-U5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="64" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="55" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="55" t="s">
+        <v>39</v>
+      </c>
+      <c r="O13" s="56"/>
+      <c r="P13" s="20"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="69"/>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L14" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="M14" s="31"/>
+      <c r="N14" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="20"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="40">
+        <v>46252</v>
+      </c>
+      <c r="B15" s="11">
+        <v>100</v>
+      </c>
+      <c r="C15" s="4">
+        <v>100</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11">
+        <f>C15/F15</f>
+        <v>12.900000007481999</v>
+      </c>
+      <c r="F15" s="13">
+        <v>7.7519379800000001</v>
+      </c>
+      <c r="G15" s="69"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="19"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="42"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="27"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="43"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="27"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="29"/>
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="43"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="29"/>
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="4">
+        <f>SUM(B15:B18)</f>
+        <v>100</v>
+      </c>
+      <c r="C19" s="4">
+        <f>SUM(C15:C18)</f>
+        <v>100</v>
+      </c>
+      <c r="D19" s="4">
+        <f>SUM(D15:D18)</f>
+        <v>0</v>
+      </c>
+      <c r="E19" s="4">
+        <f>IF(B19&gt;0,SUMPRODUCT(E15:E18,F15:F18)/SUM(F15:F18),"0.00")</f>
+        <v>12.900000007481999</v>
+      </c>
+      <c r="F19" s="13">
+        <f>SUM(F15:F18)</f>
+        <v>7.7519379800000001</v>
+      </c>
+      <c r="G19" s="70"/>
+      <c r="H19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I19" s="4">
+        <f>SUM(I15:I18)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="4">
+        <f t="shared" ref="J19:L19" si="0">SUM(J15:J18)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="5"/>
+      <c r="L19" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="33"/>
+      <c r="N19" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="O19" s="4">
+        <f>SUM(O15:O18)</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R25" s="1"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="J27" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q2:X2"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="R3:R4"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:W4"/>
+    <mergeCell ref="X3:X4"/>
+  </mergeCells>
+  <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{3CE52383-29C5-4497-90B8-DA81B24EC7D1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2426,7 +2871,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5576365-31FE-4781-A029-EABEF442854F}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2443,54 +2888,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.07</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -2525,94 +2970,94 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B14" s="50" t="s">
+      <c r="B14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="F14" s="50" t="s">
+      <c r="E14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
-      <c r="H14" s="50" t="s">
+      <c r="G14" s="69"/>
+      <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="50" t="s">
+      <c r="I14" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J14" s="50" t="s">
+      <c r="J14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="K14" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="L14" s="48" t="s">
+      <c r="K14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="L14" s="17" t="s">
         <v>1</v>
       </c>
       <c r="M14" s="31"/>
-      <c r="N14" s="49" t="s">
+      <c r="N14" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="O14" s="50" t="s">
+      <c r="O14" s="3" t="s">
         <v>29</v>
       </c>
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
+      <c r="A15" s="40">
         <v>46218</v>
       </c>
       <c r="B15" s="11">
@@ -2631,25 +3076,25 @@
       <c r="F15" s="13">
         <v>7.8382191499999996</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="24"/>
-      <c r="M15" s="52"/>
+      <c r="M15" s="19"/>
       <c r="N15" s="25"/>
       <c r="O15" s="4"/>
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -2660,13 +3105,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -2677,13 +3122,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -2694,7 +3139,7 @@
       <c r="O18" s="2"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="50" t="s">
+      <c r="A19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B19" s="4">
@@ -2717,8 +3162,8 @@
         <f>SUM(F15:F18)</f>
         <v>7.8382191499999996</v>
       </c>
-      <c r="G19" s="77"/>
-      <c r="H19" s="50" t="s">
+      <c r="G19" s="70"/>
+      <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="I19" s="4">
@@ -2735,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="M19" s="33"/>
-      <c r="N19" s="50" t="s">
+      <c r="N19" s="3" t="s">
         <v>2</v>
       </c>
       <c r="O19" s="4">
@@ -2762,6 +3207,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A12:O12"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
     <mergeCell ref="Q2:X2"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
@@ -2770,11 +3220,6 @@
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
-    <mergeCell ref="A12:O12"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{DF2B807C-B133-4C46-9D1B-D6B7BEF50215}"/>
@@ -2788,7 +3233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42AAC754-FACE-4B08-A6F5-27BDC7752425}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2805,54 +3250,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.06</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -2887,46 +3332,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -2948,7 +3393,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="69"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -2974,7 +3419,7 @@
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
+      <c r="A15" s="40">
         <v>46180</v>
       </c>
       <c r="B15" s="11">
@@ -2993,7 +3438,7 @@
       <c r="F15" s="13">
         <v>8.05542129</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3005,13 +3450,13 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3022,13 +3467,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3039,13 +3484,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3079,7 +3524,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.05542129</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3124,11 +3569,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3137,6 +3577,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{52D9614F-EF79-46CC-8F5E-FBD95649CF20}"/>
@@ -3150,7 +3595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29A7359C-5285-4575-BB13-921F668F181E}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3167,54 +3612,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.05</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -3249,46 +3694,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -3310,7 +3755,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="69"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3355,7 +3800,7 @@
       <c r="F15" s="13">
         <v>8.1859855899999996</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3367,13 +3812,13 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3384,13 +3829,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3401,13 +3846,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3441,7 +3886,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.1859855899999996</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3486,11 +3931,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3499,6 +3939,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{3C02C9E5-EA02-4BDC-91AE-416C94F85838}"/>
@@ -3512,7 +3957,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC7392A-0BC5-4BD7-983E-8A7ED64C1BD7}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3529,54 +3974,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.04</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -3611,46 +4056,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -3672,7 +4117,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="69"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -3698,7 +4143,7 @@
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
+      <c r="A15" s="40">
         <v>46131</v>
       </c>
       <c r="B15" s="11">
@@ -3717,7 +4162,7 @@
       <c r="F15" s="13">
         <v>8.6236633299999994</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -3729,13 +4174,13 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="43"/>
+      <c r="A16" s="42"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -3746,13 +4191,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="44"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -3763,13 +4208,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="44"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -3803,7 +4248,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.6236633299999994</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -3848,11 +4293,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -3861,6 +4301,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{5E453430-7CF8-4213-8F80-26238D76E7AB}"/>
@@ -3874,7 +4319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DADF1ABD-D234-4E53-B90E-0B45F09BE5A5}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3891,54 +4336,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.03</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -3973,46 +4418,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -4034,7 +4479,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="69"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4060,7 +4505,7 @@
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="41">
+      <c r="A15" s="40">
         <v>46101</v>
       </c>
       <c r="B15" s="11">
@@ -4079,7 +4524,7 @@
       <c r="F15" s="13">
         <v>9.0073860499999991</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4091,13 +4536,13 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4108,13 +4553,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4125,13 +4570,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4165,7 +4610,7 @@
         <f>SUM(F15:F18)</f>
         <v>9.0073860499999991</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4210,11 +4655,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -4223,6 +4663,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{04427A72-C2D7-400B-ACC4-6F6AA44B6641}"/>
@@ -4236,7 +4681,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4253,54 +4698,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.02</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -4335,46 +4780,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -4396,7 +4841,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="69"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4422,7 +4867,7 @@
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
+      <c r="A15" s="41">
         <v>46072</v>
       </c>
       <c r="B15" s="11">
@@ -4441,7 +4886,7 @@
       <c r="F15" s="13">
         <v>8.7032201899999997</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4453,13 +4898,13 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4470,13 +4915,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4487,13 +4932,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4527,7 +4972,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.7032201899999997</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4572,11 +5017,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="G13:G19"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="N13:O13"/>
-    <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="W3:W4"/>
     <mergeCell ref="X3:X4"/>
@@ -4585,6 +5025,11 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="G13:G19"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="N13:O13"/>
+    <mergeCell ref="Q3:Q4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12:O12" location="WEBN!A1" display="WEBN Amundi Prime ACWI Acc UCITS ETF " xr:uid="{BF7DD392-2323-41A9-A80E-2E9F0505699A}"/>
@@ -4598,7 +5043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A2:X27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4615,54 +5060,54 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q2" s="80">
+      <c r="Q2" s="73">
         <v>2026.01</v>
       </c>
-      <c r="R2" s="81"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="81"/>
-      <c r="U2" s="81"/>
-      <c r="V2" s="81"/>
-      <c r="W2" s="81"/>
-      <c r="X2" s="82"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="74"/>
+      <c r="X2" s="75"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q3" s="83" t="s">
+      <c r="Q3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="R3" s="83" t="s">
+      <c r="R3" s="76" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="83" t="s">
+      <c r="S3" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="83" t="s">
+      <c r="T3" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="U3" s="84" t="s">
+      <c r="U3" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="85"/>
-      <c r="W3" s="68" t="s">
+      <c r="V3" s="78"/>
+      <c r="W3" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="61" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="16" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="68"/>
-      <c r="X4" s="68"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="Q5" s="4">
@@ -4697,46 +5142,46 @@
       </c>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="73"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="74"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
+      <c r="F12" s="65"/>
+      <c r="G12" s="65"/>
+      <c r="H12" s="65"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="65"/>
+      <c r="K12" s="65"/>
+      <c r="L12" s="65"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="67"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="62" t="s">
+      <c r="A13" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="63"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="78" t="s">
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="I13" s="79"/>
-      <c r="J13" s="79"/>
-      <c r="K13" s="79"/>
-      <c r="L13" s="79"/>
+      <c r="I13" s="72"/>
+      <c r="J13" s="72"/>
+      <c r="K13" s="72"/>
+      <c r="L13" s="72"/>
       <c r="M13" s="30"/>
-      <c r="N13" s="62" t="s">
+      <c r="N13" s="55" t="s">
         <v>39</v>
       </c>
-      <c r="O13" s="63"/>
+      <c r="O13" s="56"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.25">
@@ -4758,7 +5203,7 @@
       <c r="F14" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="76"/>
+      <c r="G14" s="69"/>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
@@ -4784,7 +5229,7 @@
       <c r="P14" s="20"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="42">
+      <c r="A15" s="41">
         <v>46041</v>
       </c>
       <c r="B15" s="11">
@@ -4803,7 +5248,7 @@
       <c r="F15" s="13">
         <v>8.7351502399999994</v>
       </c>
-      <c r="G15" s="76"/>
+      <c r="G15" s="69"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
       <c r="J15" s="4"/>
@@ -4815,13 +5260,13 @@
       <c r="P15" s="1"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="39"/>
+      <c r="A16" s="38"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
       <c r="E16" s="5"/>
       <c r="F16" s="7"/>
-      <c r="G16" s="76"/>
+      <c r="G16" s="69"/>
       <c r="H16" s="5"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -4832,13 +5277,13 @@
       <c r="O16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="40"/>
+      <c r="A17" s="39"/>
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
       <c r="F17" s="7"/>
-      <c r="G17" s="76"/>
+      <c r="G17" s="69"/>
       <c r="H17" s="5"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -4849,13 +5294,13 @@
       <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="40"/>
+      <c r="A18" s="39"/>
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
       <c r="D18" s="5"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
-      <c r="G18" s="76"/>
+      <c r="G18" s="69"/>
       <c r="H18" s="5"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
@@ -4889,7 +5334,7 @@
         <f>SUM(F15:F18)</f>
         <v>8.7351502399999994</v>
       </c>
-      <c r="G19" s="77"/>
+      <c r="G19" s="70"/>
       <c r="H19" s="3" t="s">
         <v>2</v>
       </c>
@@ -4984,59 +5429,59 @@
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
-      <c r="W3" s="64" t="s">
+      <c r="V3" s="56"/>
+      <c r="W3" s="57" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -5070,20 +5515,20 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="65"/>
+      <c r="W4" s="58"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
@@ -5805,59 +6250,59 @@
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
-      <c r="W3" s="64" t="s">
+      <c r="V3" s="56"/>
+      <c r="W3" s="57" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -5891,20 +6336,20 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
       <c r="V4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="W4" s="65"/>
+      <c r="W4" s="58"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="e">
@@ -6414,56 +6859,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -6497,13 +6942,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -6908,56 +7353,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -6991,13 +7436,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -7303,12 +7748,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -7316,6 +7755,12 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7349,56 +7794,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -7432,13 +7877,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -7744,12 +8189,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
@@ -7757,6 +8196,12 @@
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -7790,56 +8235,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -7873,13 +8318,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -8178,56 +8623,56 @@
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="64" t="s">
+      <c r="S3" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="64" t="s">
+      <c r="T3" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="U3" s="62" t="s">
+      <c r="U3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="V3" s="63"/>
+      <c r="V3" s="56"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -8261,13 +8706,13 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="65"/>
-      <c r="T4" s="65"/>
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
       <c r="U4" s="3" t="s">
         <v>13</v>
       </c>
@@ -8520,11 +8965,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="S3:S4"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="K3:L3"/>
@@ -8533,6 +8973,11 @@
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="S3:S4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -8544,7 +8989,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AG200"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -8566,74 +9011,74 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="66"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="62" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="63"/>
-      <c r="G3" s="62" t="s">
+      <c r="F3" s="56"/>
+      <c r="G3" s="55" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="67" t="s">
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="56"/>
+      <c r="K3" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="67"/>
-      <c r="M3" s="64" t="s">
+      <c r="L3" s="60"/>
+      <c r="M3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="64" t="s">
+      <c r="Q3" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="R3" s="64" t="s">
+      <c r="R3" s="57" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="68" t="s">
+      <c r="S3" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="T3" s="68"/>
-      <c r="U3" s="68"/>
-      <c r="V3" s="62" t="s">
+      <c r="T3" s="61"/>
+      <c r="U3" s="61"/>
+      <c r="V3" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="W3" s="63"/>
-      <c r="X3" s="64" t="s">
+      <c r="W3" s="56"/>
+      <c r="X3" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="Y3" s="64" t="s">
+      <c r="Y3" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="AC3" s="68" t="s">
+      <c r="AC3" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="AD3" s="68" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="68" t="s">
+      <c r="AD3" s="61" t="s">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="61" t="s">
         <v>1</v>
       </c>
-      <c r="AF3" s="69" t="s">
+      <c r="AF3" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="AG3" s="70"/>
+      <c r="AG3" s="63"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="65"/>
+      <c r="A4" s="58"/>
       <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
@@ -8667,18 +9112,18 @@
       <c r="L4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="M4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="65"/>
-      <c r="S4" s="38" t="s">
+      <c r="M4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="T4" s="38" t="s">
+      <c r="T4" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="U4" s="38" t="s">
+      <c r="U4" s="23" t="s">
         <v>46</v>
       </c>
       <c r="V4" s="3" t="s">
@@ -8687,15 +9132,15 @@
       <c r="W4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="X4" s="65"/>
-      <c r="Y4" s="65"/>
-      <c r="AC4" s="68"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="68"/>
-      <c r="AF4" s="45" t="s">
+      <c r="X4" s="58"/>
+      <c r="Y4" s="58"/>
+      <c r="AC4" s="61"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="AG4" s="46" t="s">
+      <c r="AG4" s="45" t="s">
         <v>44</v>
       </c>
     </row>
@@ -8756,26 +9201,26 @@
       </c>
       <c r="P5" s="4">
         <f>SUM(B5:B200)</f>
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="Q5" s="13">
         <f>SUM(E5:E200)</f>
-        <v>66.900983819999993</v>
+        <v>74.701295829999992</v>
       </c>
       <c r="R5" s="4">
         <v>0</v>
       </c>
       <c r="S5" s="4">
         <f>R5-P5+X5</f>
-        <v>-800</v>
+        <v>-900</v>
       </c>
       <c r="T5" s="21">
         <f>(R5-P5+X5)/P5</f>
         <v>-1</v>
       </c>
       <c r="U5" s="21">
-        <f ca="1">XIRR(AG5:AG40,AF5:AF40)</f>
-        <v>0.23278971314430238</v>
+        <f ca="1">XIRR(AG5:AG200,AF5:AF200)</f>
+        <v>0.23258460164070127</v>
       </c>
       <c r="V5" s="4">
         <f>SUM(K5:K200)</f>
@@ -8791,7 +9236,7 @@
       </c>
       <c r="Y5" s="4" cm="1">
         <f t="array" ref="Y5">SUMPRODUCT(IFERROR(AD5:AD200,0),IFERROR(AE5:AE200,0))/SUM(IFERROR(AE5:AE200,0))</f>
-        <v>11.942568488494429</v>
+        <v>12.047983773242132</v>
       </c>
       <c r="AC5" s="4">
         <f>'2026.01'!$C$19</f>
@@ -8805,7 +9250,7 @@
         <f>'2026.01'!$F$19</f>
         <v>8.7351502399999994</v>
       </c>
-      <c r="AF5" s="47">
+      <c r="AF5" s="46">
         <f>'2026.01'!$A$15</f>
         <v>46041</v>
       </c>
@@ -8878,7 +9323,7 @@
         <f>'2026.02'!$F$19</f>
         <v>8.7032201899999997</v>
       </c>
-      <c r="AF6" s="47">
+      <c r="AF6" s="46">
         <f>'2026.02'!$A$15</f>
         <v>46072</v>
       </c>
@@ -8951,7 +9396,7 @@
         <f>'2026.03'!$F$19</f>
         <v>9.0073860499999991</v>
       </c>
-      <c r="AF7" s="47">
+      <c r="AF7" s="46">
         <f>'2026.03'!$A$15</f>
         <v>46101</v>
       </c>
@@ -9024,7 +9469,7 @@
         <f>'2026.04'!$F$19</f>
         <v>8.6236633299999994</v>
       </c>
-      <c r="AF8" s="47">
+      <c r="AF8" s="46">
         <f>'2026.04'!$A$15</f>
         <v>46131</v>
       </c>
@@ -9097,7 +9542,7 @@
         <f>'2026.05'!$F$19</f>
         <v>8.1859855899999996</v>
       </c>
-      <c r="AF9" s="47">
+      <c r="AF9" s="46">
         <f>'2026.05'!$A$15</f>
         <v>46161</v>
       </c>
@@ -9131,7 +9576,7 @@
         <f t="shared" si="4"/>
         <v>51.310826689999999</v>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="7">
         <v>12.78</v>
       </c>
       <c r="H10" s="4">
@@ -9170,7 +9615,7 @@
         <f>'2026.06'!$F$19</f>
         <v>8.05542129</v>
       </c>
-      <c r="AF10" s="47">
+      <c r="AF10" s="46">
         <f>'2026.06'!$A$15</f>
         <v>46180</v>
       </c>
@@ -9204,7 +9649,7 @@
         <f t="shared" si="4"/>
         <v>59.149045839999999</v>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="7">
         <v>12.592000000000001</v>
       </c>
       <c r="H11" s="4">
@@ -9243,7 +9688,7 @@
         <f>'2026.07'!$F$19</f>
         <v>7.8382191499999996</v>
       </c>
-      <c r="AF11" s="47">
+      <c r="AF11" s="46">
         <f>'2026.07'!$A$15</f>
         <v>46218</v>
       </c>
@@ -9277,7 +9722,7 @@
         <f t="shared" ref="F12" si="9">E12+F11</f>
         <v>66.900983819999993</v>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="7">
         <v>12.86</v>
       </c>
       <c r="H12" s="4">
@@ -9305,45 +9750,98 @@
         <v>0</v>
       </c>
       <c r="AC12" s="4">
-        <f>'2026.07'!$C$19</f>
+        <f>'2026.08'!$C$19</f>
         <v>100</v>
       </c>
       <c r="AD12" s="4">
-        <f>'2026.07'!$E$19</f>
-        <v>12.758000010754994</v>
+        <f>'2026.08'!$E$19</f>
+        <v>12.900000007481999</v>
       </c>
       <c r="AE12" s="5">
-        <f>'2026.07'!$F$19</f>
-        <v>7.8382191499999996</v>
-      </c>
-      <c r="AF12" s="47">
-        <f>'2026.07'!$A$15</f>
-        <v>46218</v>
+        <f>'2026.08'!$F$19</f>
+        <v>7.7519379800000001</v>
+      </c>
+      <c r="AF12" s="46">
+        <f>'2026.08'!$A$15</f>
+        <v>46252</v>
       </c>
       <c r="AG12" s="4">
-        <f>'2026.07'!$B$15*-1</f>
+        <f>'2026.08'!$B$15*-1</f>
         <v>-100</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="2"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="13"/>
-      <c r="AF13" s="47"/>
-      <c r="AG13" s="4"/>
+      <c r="A13" s="36">
+        <f>'2026.09'!$Q$2</f>
+        <v>2026.09</v>
+      </c>
+      <c r="B13" s="4">
+        <f>'2026.09'!$B$15</f>
+        <v>100</v>
+      </c>
+      <c r="C13" s="4">
+        <f>'2026.09'!$C$15</f>
+        <v>100</v>
+      </c>
+      <c r="D13" s="4">
+        <f t="shared" ref="D13" si="13">C13+D12</f>
+        <v>900</v>
+      </c>
+      <c r="E13" s="13">
+        <f>'2026.09'!$F$15</f>
+        <v>7.8003120099999999</v>
+      </c>
+      <c r="F13" s="13">
+        <f t="shared" ref="F13" si="14">E13+F12</f>
+        <v>74.701295829999992</v>
+      </c>
+      <c r="G13" s="79">
+        <v>13.044</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" ref="H13" si="15">F13*G13</f>
+        <v>974.40370280651996</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" ref="I13" si="16">H13-D13</f>
+        <v>74.403702806519959</v>
+      </c>
+      <c r="J13" s="21">
+        <f t="shared" ref="J13" si="17">(H13-D13)/D13</f>
+        <v>8.2670780896133292E-2</v>
+      </c>
+      <c r="K13" s="4">
+        <f>'2026.09'!$D$15</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="4">
+        <f>'2026.09'!$J$15</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="4">
+        <f>'2026.09'!$O$15</f>
+        <v>0</v>
+      </c>
+      <c r="AC13" s="4">
+        <f>'2026.09'!$C$19</f>
+        <v>100</v>
+      </c>
+      <c r="AD13" s="4">
+        <f>'2026.09'!$E$19</f>
+        <v>12.820000004076761</v>
+      </c>
+      <c r="AE13" s="5">
+        <f>'2026.09'!$F$19</f>
+        <v>7.8003120099999999</v>
+      </c>
+      <c r="AF13" s="46">
+        <f>'2026.09'!$A$15</f>
+        <v>46275</v>
+      </c>
+      <c r="AG13" s="4">
+        <f>'2026.09'!$B$15*-1</f>
+        <v>-100</v>
+      </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
@@ -9362,7 +9860,7 @@
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="5"/>
-      <c r="AF14" s="47"/>
+      <c r="AF14" s="46"/>
       <c r="AG14" s="4"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
@@ -9382,7 +9880,7 @@
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="5"/>
-      <c r="AF15" s="47"/>
+      <c r="AF15" s="46"/>
       <c r="AG15" s="4"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
@@ -9402,7 +9900,7 @@
       <c r="AC16" s="5"/>
       <c r="AD16" s="5"/>
       <c r="AE16" s="5"/>
-      <c r="AF16" s="47"/>
+      <c r="AF16" s="46"/>
       <c r="AG16" s="4"/>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
@@ -9422,7 +9920,7 @@
       <c r="AC17" s="5"/>
       <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
-      <c r="AF17" s="47"/>
+      <c r="AF17" s="46"/>
       <c r="AG17" s="4"/>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
@@ -9442,7 +9940,7 @@
       <c r="AC18" s="5"/>
       <c r="AD18" s="5"/>
       <c r="AE18" s="5"/>
-      <c r="AF18" s="47"/>
+      <c r="AF18" s="46"/>
       <c r="AG18" s="4"/>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
@@ -9462,7 +9960,7 @@
       <c r="AC19" s="5"/>
       <c r="AD19" s="5"/>
       <c r="AE19" s="5"/>
-      <c r="AF19" s="47"/>
+      <c r="AF19" s="46"/>
       <c r="AG19" s="4"/>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
@@ -9482,7 +9980,7 @@
       <c r="AC20" s="5"/>
       <c r="AD20" s="5"/>
       <c r="AE20" s="5"/>
-      <c r="AF20" s="47"/>
+      <c r="AF20" s="46"/>
       <c r="AG20" s="4"/>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
@@ -9502,140 +10000,1288 @@
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5"/>
-      <c r="AF21" s="47"/>
+      <c r="AF21" s="46"/>
       <c r="AG21" s="4"/>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5"/>
-      <c r="AF22" s="47"/>
+      <c r="AF22" s="46"/>
       <c r="AG22" s="4"/>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC23" s="5"/>
       <c r="AD23" s="5"/>
       <c r="AE23" s="5"/>
-      <c r="AF23" s="47"/>
+      <c r="AF23" s="46"/>
       <c r="AG23" s="4"/>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC24" s="5"/>
       <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
-      <c r="AF24" s="47"/>
+      <c r="AF24" s="46"/>
       <c r="AG24" s="4"/>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC25" s="5"/>
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
-      <c r="AF25" s="47"/>
+      <c r="AF25" s="46"/>
       <c r="AG25" s="4"/>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC26" s="5"/>
       <c r="AD26" s="5"/>
       <c r="AE26" s="5"/>
-      <c r="AF26" s="47"/>
+      <c r="AF26" s="46"/>
       <c r="AG26" s="4"/>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC27" s="5"/>
       <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
-      <c r="AF27" s="47"/>
+      <c r="AF27" s="46"/>
       <c r="AG27" s="4"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC28" s="5"/>
       <c r="AD28" s="5"/>
       <c r="AE28" s="5"/>
-      <c r="AF28" s="47"/>
+      <c r="AF28" s="46"/>
       <c r="AG28" s="4"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC29" s="5"/>
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
-      <c r="AF29" s="47"/>
+      <c r="AF29" s="46"/>
       <c r="AG29" s="4"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC30" s="5"/>
       <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
-      <c r="AF30" s="47"/>
+      <c r="AF30" s="46"/>
       <c r="AG30" s="4"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC31" s="5"/>
       <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
-      <c r="AF31" s="47"/>
+      <c r="AF31" s="46"/>
       <c r="AG31" s="4"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
       <c r="AE32" s="5"/>
-      <c r="AF32" s="47"/>
+      <c r="AF32" s="46"/>
       <c r="AG32" s="4"/>
     </row>
     <row r="33" spans="29:33" x14ac:dyDescent="0.25">
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
-      <c r="AF33" s="47"/>
+      <c r="AF33" s="46"/>
       <c r="AG33" s="4"/>
     </row>
     <row r="34" spans="29:33" x14ac:dyDescent="0.25">
       <c r="AC34" s="5"/>
       <c r="AD34" s="5"/>
       <c r="AE34" s="5"/>
-      <c r="AF34" s="47"/>
+      <c r="AF34" s="46"/>
       <c r="AG34" s="4"/>
     </row>
     <row r="35" spans="29:33" x14ac:dyDescent="0.25">
       <c r="AC35" s="5"/>
       <c r="AD35" s="5"/>
       <c r="AE35" s="5"/>
-      <c r="AF35" s="47"/>
+      <c r="AF35" s="46"/>
       <c r="AG35" s="4"/>
     </row>
     <row r="36" spans="29:33" x14ac:dyDescent="0.25">
       <c r="AC36" s="5"/>
       <c r="AD36" s="5"/>
       <c r="AE36" s="5"/>
-      <c r="AF36" s="47">
+      <c r="AF36" s="46"/>
+      <c r="AG36" s="4"/>
+    </row>
+    <row r="37" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2"/>
+      <c r="AE37" s="2"/>
+      <c r="AF37" s="2"/>
+      <c r="AG37" s="2"/>
+    </row>
+    <row r="38" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2"/>
+      <c r="AF38" s="2"/>
+      <c r="AG38" s="2"/>
+    </row>
+    <row r="39" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="2"/>
+      <c r="AE39" s="2"/>
+      <c r="AF39" s="2"/>
+      <c r="AG39" s="2"/>
+    </row>
+    <row r="40" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="2"/>
+      <c r="AE40" s="2"/>
+      <c r="AF40" s="2"/>
+      <c r="AG40" s="2"/>
+    </row>
+    <row r="41" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="2"/>
+      <c r="AE41" s="2"/>
+      <c r="AF41" s="2"/>
+      <c r="AG41" s="2"/>
+    </row>
+    <row r="42" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="2"/>
+      <c r="AE42" s="2"/>
+      <c r="AF42" s="2"/>
+      <c r="AG42" s="2"/>
+    </row>
+    <row r="43" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="2"/>
+      <c r="AE43" s="2"/>
+      <c r="AF43" s="2"/>
+      <c r="AG43" s="2"/>
+    </row>
+    <row r="44" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="2"/>
+      <c r="AE44" s="2"/>
+      <c r="AF44" s="2"/>
+      <c r="AG44" s="2"/>
+    </row>
+    <row r="45" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="2"/>
+      <c r="AE45" s="2"/>
+      <c r="AF45" s="2"/>
+      <c r="AG45" s="2"/>
+    </row>
+    <row r="46" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="2"/>
+      <c r="AE46" s="2"/>
+      <c r="AF46" s="2"/>
+      <c r="AG46" s="2"/>
+    </row>
+    <row r="47" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="2"/>
+      <c r="AE47" s="2"/>
+      <c r="AF47" s="2"/>
+      <c r="AG47" s="2"/>
+    </row>
+    <row r="48" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="2"/>
+      <c r="AE48" s="2"/>
+      <c r="AF48" s="2"/>
+      <c r="AG48" s="2"/>
+    </row>
+    <row r="49" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="2"/>
+      <c r="AE49" s="2"/>
+      <c r="AF49" s="2"/>
+      <c r="AG49" s="2"/>
+    </row>
+    <row r="50" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="2"/>
+      <c r="AE50" s="2"/>
+      <c r="AF50" s="2"/>
+      <c r="AG50" s="2"/>
+    </row>
+    <row r="51" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC51" s="2"/>
+      <c r="AD51" s="2"/>
+      <c r="AE51" s="2"/>
+      <c r="AF51" s="2"/>
+      <c r="AG51" s="2"/>
+    </row>
+    <row r="52" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC52" s="2"/>
+      <c r="AD52" s="2"/>
+      <c r="AE52" s="2"/>
+      <c r="AF52" s="2"/>
+      <c r="AG52" s="2"/>
+    </row>
+    <row r="53" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC53" s="2"/>
+      <c r="AD53" s="2"/>
+      <c r="AE53" s="2"/>
+      <c r="AF53" s="2"/>
+      <c r="AG53" s="2"/>
+    </row>
+    <row r="54" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC54" s="2"/>
+      <c r="AD54" s="2"/>
+      <c r="AE54" s="2"/>
+      <c r="AF54" s="2"/>
+      <c r="AG54" s="2"/>
+    </row>
+    <row r="55" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC55" s="2"/>
+      <c r="AD55" s="2"/>
+      <c r="AE55" s="2"/>
+      <c r="AF55" s="2"/>
+      <c r="AG55" s="2"/>
+    </row>
+    <row r="56" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC56" s="2"/>
+      <c r="AD56" s="2"/>
+      <c r="AE56" s="2"/>
+      <c r="AF56" s="2"/>
+      <c r="AG56" s="2"/>
+    </row>
+    <row r="57" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC57" s="2"/>
+      <c r="AD57" s="2"/>
+      <c r="AE57" s="2"/>
+      <c r="AF57" s="2"/>
+      <c r="AG57" s="2"/>
+    </row>
+    <row r="58" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC58" s="2"/>
+      <c r="AD58" s="2"/>
+      <c r="AE58" s="2"/>
+      <c r="AF58" s="2"/>
+      <c r="AG58" s="2"/>
+    </row>
+    <row r="59" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC59" s="2"/>
+      <c r="AD59" s="2"/>
+      <c r="AE59" s="2"/>
+      <c r="AF59" s="2"/>
+      <c r="AG59" s="2"/>
+    </row>
+    <row r="60" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC60" s="2"/>
+      <c r="AD60" s="2"/>
+      <c r="AE60" s="2"/>
+      <c r="AF60" s="2"/>
+      <c r="AG60" s="2"/>
+    </row>
+    <row r="61" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC61" s="2"/>
+      <c r="AD61" s="2"/>
+      <c r="AE61" s="2"/>
+      <c r="AF61" s="2"/>
+      <c r="AG61" s="2"/>
+    </row>
+    <row r="62" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC62" s="2"/>
+      <c r="AD62" s="2"/>
+      <c r="AE62" s="2"/>
+      <c r="AF62" s="2"/>
+      <c r="AG62" s="2"/>
+    </row>
+    <row r="63" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC63" s="2"/>
+      <c r="AD63" s="2"/>
+      <c r="AE63" s="2"/>
+      <c r="AF63" s="2"/>
+      <c r="AG63" s="2"/>
+    </row>
+    <row r="64" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC64" s="2"/>
+      <c r="AD64" s="2"/>
+      <c r="AE64" s="2"/>
+      <c r="AF64" s="2"/>
+      <c r="AG64" s="2"/>
+    </row>
+    <row r="65" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC65" s="2"/>
+      <c r="AD65" s="2"/>
+      <c r="AE65" s="2"/>
+      <c r="AF65" s="2"/>
+      <c r="AG65" s="2"/>
+    </row>
+    <row r="66" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC66" s="2"/>
+      <c r="AD66" s="2"/>
+      <c r="AE66" s="2"/>
+      <c r="AF66" s="2"/>
+      <c r="AG66" s="2"/>
+    </row>
+    <row r="67" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC67" s="2"/>
+      <c r="AD67" s="2"/>
+      <c r="AE67" s="2"/>
+      <c r="AF67" s="2"/>
+      <c r="AG67" s="2"/>
+    </row>
+    <row r="68" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC68" s="2"/>
+      <c r="AD68" s="2"/>
+      <c r="AE68" s="2"/>
+      <c r="AF68" s="2"/>
+      <c r="AG68" s="2"/>
+    </row>
+    <row r="69" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC69" s="2"/>
+      <c r="AD69" s="2"/>
+      <c r="AE69" s="2"/>
+      <c r="AF69" s="2"/>
+      <c r="AG69" s="2"/>
+    </row>
+    <row r="70" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC70" s="2"/>
+      <c r="AD70" s="2"/>
+      <c r="AE70" s="2"/>
+      <c r="AF70" s="2"/>
+      <c r="AG70" s="2"/>
+    </row>
+    <row r="71" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC71" s="2"/>
+      <c r="AD71" s="2"/>
+      <c r="AE71" s="2"/>
+      <c r="AF71" s="2"/>
+      <c r="AG71" s="2"/>
+    </row>
+    <row r="72" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC72" s="2"/>
+      <c r="AD72" s="2"/>
+      <c r="AE72" s="2"/>
+      <c r="AF72" s="2"/>
+      <c r="AG72" s="2"/>
+    </row>
+    <row r="73" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC73" s="2"/>
+      <c r="AD73" s="2"/>
+      <c r="AE73" s="2"/>
+      <c r="AF73" s="2"/>
+      <c r="AG73" s="2"/>
+    </row>
+    <row r="74" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC74" s="2"/>
+      <c r="AD74" s="2"/>
+      <c r="AE74" s="2"/>
+      <c r="AF74" s="2"/>
+      <c r="AG74" s="2"/>
+    </row>
+    <row r="75" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC75" s="2"/>
+      <c r="AD75" s="2"/>
+      <c r="AE75" s="2"/>
+      <c r="AF75" s="2"/>
+      <c r="AG75" s="2"/>
+    </row>
+    <row r="76" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC76" s="2"/>
+      <c r="AD76" s="2"/>
+      <c r="AE76" s="2"/>
+      <c r="AF76" s="2"/>
+      <c r="AG76" s="2"/>
+    </row>
+    <row r="77" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC77" s="2"/>
+      <c r="AD77" s="2"/>
+      <c r="AE77" s="2"/>
+      <c r="AF77" s="2"/>
+      <c r="AG77" s="2"/>
+    </row>
+    <row r="78" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC78" s="2"/>
+      <c r="AD78" s="2"/>
+      <c r="AE78" s="2"/>
+      <c r="AF78" s="2"/>
+      <c r="AG78" s="2"/>
+    </row>
+    <row r="79" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC79" s="2"/>
+      <c r="AD79" s="2"/>
+      <c r="AE79" s="2"/>
+      <c r="AF79" s="2"/>
+      <c r="AG79" s="2"/>
+    </row>
+    <row r="80" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC80" s="2"/>
+      <c r="AD80" s="2"/>
+      <c r="AE80" s="2"/>
+      <c r="AF80" s="2"/>
+      <c r="AG80" s="2"/>
+    </row>
+    <row r="81" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC81" s="2"/>
+      <c r="AD81" s="2"/>
+      <c r="AE81" s="2"/>
+      <c r="AF81" s="2"/>
+      <c r="AG81" s="2"/>
+    </row>
+    <row r="82" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC82" s="2"/>
+      <c r="AD82" s="2"/>
+      <c r="AE82" s="2"/>
+      <c r="AF82" s="2"/>
+      <c r="AG82" s="2"/>
+    </row>
+    <row r="83" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC83" s="2"/>
+      <c r="AD83" s="2"/>
+      <c r="AE83" s="2"/>
+      <c r="AF83" s="2"/>
+      <c r="AG83" s="2"/>
+    </row>
+    <row r="84" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC84" s="2"/>
+      <c r="AD84" s="2"/>
+      <c r="AE84" s="2"/>
+      <c r="AF84" s="2"/>
+      <c r="AG84" s="2"/>
+    </row>
+    <row r="85" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC85" s="2"/>
+      <c r="AD85" s="2"/>
+      <c r="AE85" s="2"/>
+      <c r="AF85" s="2"/>
+      <c r="AG85" s="2"/>
+    </row>
+    <row r="86" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC86" s="2"/>
+      <c r="AD86" s="2"/>
+      <c r="AE86" s="2"/>
+      <c r="AF86" s="2"/>
+      <c r="AG86" s="2"/>
+    </row>
+    <row r="87" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC87" s="2"/>
+      <c r="AD87" s="2"/>
+      <c r="AE87" s="2"/>
+      <c r="AF87" s="2"/>
+      <c r="AG87" s="2"/>
+    </row>
+    <row r="88" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC88" s="2"/>
+      <c r="AD88" s="2"/>
+      <c r="AE88" s="2"/>
+      <c r="AF88" s="2"/>
+      <c r="AG88" s="2"/>
+    </row>
+    <row r="89" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC89" s="2"/>
+      <c r="AD89" s="2"/>
+      <c r="AE89" s="2"/>
+      <c r="AF89" s="2"/>
+      <c r="AG89" s="2"/>
+    </row>
+    <row r="90" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC90" s="2"/>
+      <c r="AD90" s="2"/>
+      <c r="AE90" s="2"/>
+      <c r="AF90" s="2"/>
+      <c r="AG90" s="2"/>
+    </row>
+    <row r="91" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC91" s="2"/>
+      <c r="AD91" s="2"/>
+      <c r="AE91" s="2"/>
+      <c r="AF91" s="2"/>
+      <c r="AG91" s="2"/>
+    </row>
+    <row r="92" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC92" s="2"/>
+      <c r="AD92" s="2"/>
+      <c r="AE92" s="2"/>
+      <c r="AF92" s="2"/>
+      <c r="AG92" s="2"/>
+    </row>
+    <row r="93" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC93" s="2"/>
+      <c r="AD93" s="2"/>
+      <c r="AE93" s="2"/>
+      <c r="AF93" s="2"/>
+      <c r="AG93" s="2"/>
+    </row>
+    <row r="94" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC94" s="2"/>
+      <c r="AD94" s="2"/>
+      <c r="AE94" s="2"/>
+      <c r="AF94" s="2"/>
+      <c r="AG94" s="2"/>
+    </row>
+    <row r="95" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC95" s="2"/>
+      <c r="AD95" s="2"/>
+      <c r="AE95" s="2"/>
+      <c r="AF95" s="2"/>
+      <c r="AG95" s="2"/>
+    </row>
+    <row r="96" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC96" s="2"/>
+      <c r="AD96" s="2"/>
+      <c r="AE96" s="2"/>
+      <c r="AF96" s="2"/>
+      <c r="AG96" s="2"/>
+    </row>
+    <row r="97" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC97" s="2"/>
+      <c r="AD97" s="2"/>
+      <c r="AE97" s="2"/>
+      <c r="AF97" s="2"/>
+      <c r="AG97" s="2"/>
+    </row>
+    <row r="98" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC98" s="2"/>
+      <c r="AD98" s="2"/>
+      <c r="AE98" s="2"/>
+      <c r="AF98" s="2"/>
+      <c r="AG98" s="2"/>
+    </row>
+    <row r="99" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC99" s="2"/>
+      <c r="AD99" s="2"/>
+      <c r="AE99" s="2"/>
+      <c r="AF99" s="2"/>
+      <c r="AG99" s="2"/>
+    </row>
+    <row r="100" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC100" s="2"/>
+      <c r="AD100" s="2"/>
+      <c r="AE100" s="2"/>
+      <c r="AF100" s="2"/>
+      <c r="AG100" s="2"/>
+    </row>
+    <row r="101" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC101" s="2"/>
+      <c r="AD101" s="2"/>
+      <c r="AE101" s="2"/>
+      <c r="AF101" s="2"/>
+      <c r="AG101" s="2"/>
+    </row>
+    <row r="102" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC102" s="2"/>
+      <c r="AD102" s="2"/>
+      <c r="AE102" s="2"/>
+      <c r="AF102" s="2"/>
+      <c r="AG102" s="2"/>
+    </row>
+    <row r="103" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC103" s="2"/>
+      <c r="AD103" s="2"/>
+      <c r="AE103" s="2"/>
+      <c r="AF103" s="2"/>
+      <c r="AG103" s="2"/>
+    </row>
+    <row r="104" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC104" s="2"/>
+      <c r="AD104" s="2"/>
+      <c r="AE104" s="2"/>
+      <c r="AF104" s="2"/>
+      <c r="AG104" s="2"/>
+    </row>
+    <row r="105" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC105" s="2"/>
+      <c r="AD105" s="2"/>
+      <c r="AE105" s="2"/>
+      <c r="AF105" s="2"/>
+      <c r="AG105" s="2"/>
+    </row>
+    <row r="106" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC106" s="2"/>
+      <c r="AD106" s="2"/>
+      <c r="AE106" s="2"/>
+      <c r="AF106" s="2"/>
+      <c r="AG106" s="2"/>
+    </row>
+    <row r="107" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC107" s="2"/>
+      <c r="AD107" s="2"/>
+      <c r="AE107" s="2"/>
+      <c r="AF107" s="2"/>
+      <c r="AG107" s="2"/>
+    </row>
+    <row r="108" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC108" s="2"/>
+      <c r="AD108" s="2"/>
+      <c r="AE108" s="2"/>
+      <c r="AF108" s="2"/>
+      <c r="AG108" s="2"/>
+    </row>
+    <row r="109" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC109" s="2"/>
+      <c r="AD109" s="2"/>
+      <c r="AE109" s="2"/>
+      <c r="AF109" s="2"/>
+      <c r="AG109" s="2"/>
+    </row>
+    <row r="110" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC110" s="2"/>
+      <c r="AD110" s="2"/>
+      <c r="AE110" s="2"/>
+      <c r="AF110" s="2"/>
+      <c r="AG110" s="2"/>
+    </row>
+    <row r="111" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC111" s="2"/>
+      <c r="AD111" s="2"/>
+      <c r="AE111" s="2"/>
+      <c r="AF111" s="2"/>
+      <c r="AG111" s="2"/>
+    </row>
+    <row r="112" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC112" s="2"/>
+      <c r="AD112" s="2"/>
+      <c r="AE112" s="2"/>
+      <c r="AF112" s="2"/>
+      <c r="AG112" s="2"/>
+    </row>
+    <row r="113" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC113" s="2"/>
+      <c r="AD113" s="2"/>
+      <c r="AE113" s="2"/>
+      <c r="AF113" s="2"/>
+      <c r="AG113" s="2"/>
+    </row>
+    <row r="114" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC114" s="2"/>
+      <c r="AD114" s="2"/>
+      <c r="AE114" s="2"/>
+      <c r="AF114" s="2"/>
+      <c r="AG114" s="2"/>
+    </row>
+    <row r="115" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC115" s="2"/>
+      <c r="AD115" s="2"/>
+      <c r="AE115" s="2"/>
+      <c r="AF115" s="2"/>
+      <c r="AG115" s="2"/>
+    </row>
+    <row r="116" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC116" s="2"/>
+      <c r="AD116" s="2"/>
+      <c r="AE116" s="2"/>
+      <c r="AF116" s="2"/>
+      <c r="AG116" s="2"/>
+    </row>
+    <row r="117" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC117" s="2"/>
+      <c r="AD117" s="2"/>
+      <c r="AE117" s="2"/>
+      <c r="AF117" s="2"/>
+      <c r="AG117" s="2"/>
+    </row>
+    <row r="118" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC118" s="2"/>
+      <c r="AD118" s="2"/>
+      <c r="AE118" s="2"/>
+      <c r="AF118" s="2"/>
+      <c r="AG118" s="2"/>
+    </row>
+    <row r="119" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC119" s="2"/>
+      <c r="AD119" s="2"/>
+      <c r="AE119" s="2"/>
+      <c r="AF119" s="2"/>
+      <c r="AG119" s="2"/>
+    </row>
+    <row r="120" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC120" s="2"/>
+      <c r="AD120" s="2"/>
+      <c r="AE120" s="2"/>
+      <c r="AF120" s="2"/>
+      <c r="AG120" s="2"/>
+    </row>
+    <row r="121" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC121" s="2"/>
+      <c r="AD121" s="2"/>
+      <c r="AE121" s="2"/>
+      <c r="AF121" s="2"/>
+      <c r="AG121" s="2"/>
+    </row>
+    <row r="122" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC122" s="2"/>
+      <c r="AD122" s="2"/>
+      <c r="AE122" s="2"/>
+      <c r="AF122" s="2"/>
+      <c r="AG122" s="2"/>
+    </row>
+    <row r="123" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC123" s="2"/>
+      <c r="AD123" s="2"/>
+      <c r="AE123" s="2"/>
+      <c r="AF123" s="2"/>
+      <c r="AG123" s="2"/>
+    </row>
+    <row r="124" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC124" s="2"/>
+      <c r="AD124" s="2"/>
+      <c r="AE124" s="2"/>
+      <c r="AF124" s="2"/>
+      <c r="AG124" s="2"/>
+    </row>
+    <row r="125" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC125" s="2"/>
+      <c r="AD125" s="2"/>
+      <c r="AE125" s="2"/>
+      <c r="AF125" s="2"/>
+      <c r="AG125" s="2"/>
+    </row>
+    <row r="126" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC126" s="2"/>
+      <c r="AD126" s="2"/>
+      <c r="AE126" s="2"/>
+      <c r="AF126" s="2"/>
+      <c r="AG126" s="2"/>
+    </row>
+    <row r="127" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC127" s="2"/>
+      <c r="AD127" s="2"/>
+      <c r="AE127" s="2"/>
+      <c r="AF127" s="2"/>
+      <c r="AG127" s="2"/>
+    </row>
+    <row r="128" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC128" s="2"/>
+      <c r="AD128" s="2"/>
+      <c r="AE128" s="2"/>
+      <c r="AF128" s="2"/>
+      <c r="AG128" s="2"/>
+    </row>
+    <row r="129" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC129" s="2"/>
+      <c r="AD129" s="2"/>
+      <c r="AE129" s="2"/>
+      <c r="AF129" s="2"/>
+      <c r="AG129" s="2"/>
+    </row>
+    <row r="130" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC130" s="2"/>
+      <c r="AD130" s="2"/>
+      <c r="AE130" s="2"/>
+      <c r="AF130" s="2"/>
+      <c r="AG130" s="2"/>
+    </row>
+    <row r="131" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC131" s="2"/>
+      <c r="AD131" s="2"/>
+      <c r="AE131" s="2"/>
+      <c r="AF131" s="2"/>
+      <c r="AG131" s="2"/>
+    </row>
+    <row r="132" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC132" s="2"/>
+      <c r="AD132" s="2"/>
+      <c r="AE132" s="2"/>
+      <c r="AF132" s="2"/>
+      <c r="AG132" s="2"/>
+    </row>
+    <row r="133" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC133" s="2"/>
+      <c r="AD133" s="2"/>
+      <c r="AE133" s="2"/>
+      <c r="AF133" s="2"/>
+      <c r="AG133" s="2"/>
+    </row>
+    <row r="134" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC134" s="2"/>
+      <c r="AD134" s="2"/>
+      <c r="AE134" s="2"/>
+      <c r="AF134" s="2"/>
+      <c r="AG134" s="2"/>
+    </row>
+    <row r="135" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC135" s="2"/>
+      <c r="AD135" s="2"/>
+      <c r="AE135" s="2"/>
+      <c r="AF135" s="2"/>
+      <c r="AG135" s="2"/>
+    </row>
+    <row r="136" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC136" s="2"/>
+      <c r="AD136" s="2"/>
+      <c r="AE136" s="2"/>
+      <c r="AF136" s="2"/>
+      <c r="AG136" s="2"/>
+    </row>
+    <row r="137" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC137" s="2"/>
+      <c r="AD137" s="2"/>
+      <c r="AE137" s="2"/>
+      <c r="AF137" s="2"/>
+      <c r="AG137" s="2"/>
+    </row>
+    <row r="138" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC138" s="2"/>
+      <c r="AD138" s="2"/>
+      <c r="AE138" s="2"/>
+      <c r="AF138" s="2"/>
+      <c r="AG138" s="2"/>
+    </row>
+    <row r="139" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC139" s="2"/>
+      <c r="AD139" s="2"/>
+      <c r="AE139" s="2"/>
+      <c r="AF139" s="2"/>
+      <c r="AG139" s="2"/>
+    </row>
+    <row r="140" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC140" s="2"/>
+      <c r="AD140" s="2"/>
+      <c r="AE140" s="2"/>
+      <c r="AF140" s="2"/>
+      <c r="AG140" s="2"/>
+    </row>
+    <row r="141" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC141" s="2"/>
+      <c r="AD141" s="2"/>
+      <c r="AE141" s="2"/>
+      <c r="AF141" s="2"/>
+      <c r="AG141" s="2"/>
+    </row>
+    <row r="142" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC142" s="2"/>
+      <c r="AD142" s="2"/>
+      <c r="AE142" s="2"/>
+      <c r="AF142" s="2"/>
+      <c r="AG142" s="2"/>
+    </row>
+    <row r="143" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC143" s="2"/>
+      <c r="AD143" s="2"/>
+      <c r="AE143" s="2"/>
+      <c r="AF143" s="2"/>
+      <c r="AG143" s="2"/>
+    </row>
+    <row r="144" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC144" s="2"/>
+      <c r="AD144" s="2"/>
+      <c r="AE144" s="2"/>
+      <c r="AF144" s="2"/>
+      <c r="AG144" s="2"/>
+    </row>
+    <row r="145" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC145" s="2"/>
+      <c r="AD145" s="2"/>
+      <c r="AE145" s="2"/>
+      <c r="AF145" s="2"/>
+      <c r="AG145" s="2"/>
+    </row>
+    <row r="146" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC146" s="2"/>
+      <c r="AD146" s="2"/>
+      <c r="AE146" s="2"/>
+      <c r="AF146" s="2"/>
+      <c r="AG146" s="2"/>
+    </row>
+    <row r="147" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC147" s="2"/>
+      <c r="AD147" s="2"/>
+      <c r="AE147" s="2"/>
+      <c r="AF147" s="2"/>
+      <c r="AG147" s="2"/>
+    </row>
+    <row r="148" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC148" s="2"/>
+      <c r="AD148" s="2"/>
+      <c r="AE148" s="2"/>
+      <c r="AF148" s="2"/>
+      <c r="AG148" s="2"/>
+    </row>
+    <row r="149" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC149" s="2"/>
+      <c r="AD149" s="2"/>
+      <c r="AE149" s="2"/>
+      <c r="AF149" s="2"/>
+      <c r="AG149" s="2"/>
+    </row>
+    <row r="150" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC150" s="2"/>
+      <c r="AD150" s="2"/>
+      <c r="AE150" s="2"/>
+      <c r="AF150" s="2"/>
+      <c r="AG150" s="2"/>
+    </row>
+    <row r="151" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC151" s="2"/>
+      <c r="AD151" s="2"/>
+      <c r="AE151" s="2"/>
+      <c r="AF151" s="2"/>
+      <c r="AG151" s="2"/>
+    </row>
+    <row r="152" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC152" s="2"/>
+      <c r="AD152" s="2"/>
+      <c r="AE152" s="2"/>
+      <c r="AF152" s="2"/>
+      <c r="AG152" s="2"/>
+    </row>
+    <row r="153" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC153" s="2"/>
+      <c r="AD153" s="2"/>
+      <c r="AE153" s="2"/>
+      <c r="AF153" s="2"/>
+      <c r="AG153" s="2"/>
+    </row>
+    <row r="154" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC154" s="2"/>
+      <c r="AD154" s="2"/>
+      <c r="AE154" s="2"/>
+      <c r="AF154" s="2"/>
+      <c r="AG154" s="2"/>
+    </row>
+    <row r="155" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC155" s="2"/>
+      <c r="AD155" s="2"/>
+      <c r="AE155" s="2"/>
+      <c r="AF155" s="2"/>
+      <c r="AG155" s="2"/>
+    </row>
+    <row r="156" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC156" s="2"/>
+      <c r="AD156" s="2"/>
+      <c r="AE156" s="2"/>
+      <c r="AF156" s="2"/>
+      <c r="AG156" s="2"/>
+    </row>
+    <row r="157" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC157" s="2"/>
+      <c r="AD157" s="2"/>
+      <c r="AE157" s="2"/>
+      <c r="AF157" s="2"/>
+      <c r="AG157" s="2"/>
+    </row>
+    <row r="158" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC158" s="2"/>
+      <c r="AD158" s="2"/>
+      <c r="AE158" s="2"/>
+      <c r="AF158" s="2"/>
+      <c r="AG158" s="2"/>
+    </row>
+    <row r="159" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC159" s="2"/>
+      <c r="AD159" s="2"/>
+      <c r="AE159" s="2"/>
+      <c r="AF159" s="2"/>
+      <c r="AG159" s="2"/>
+    </row>
+    <row r="160" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC160" s="2"/>
+      <c r="AD160" s="2"/>
+      <c r="AE160" s="2"/>
+      <c r="AF160" s="2"/>
+      <c r="AG160" s="2"/>
+    </row>
+    <row r="161" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC161" s="2"/>
+      <c r="AD161" s="2"/>
+      <c r="AE161" s="2"/>
+      <c r="AF161" s="2"/>
+      <c r="AG161" s="2"/>
+    </row>
+    <row r="162" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC162" s="2"/>
+      <c r="AD162" s="2"/>
+      <c r="AE162" s="2"/>
+      <c r="AF162" s="2"/>
+      <c r="AG162" s="2"/>
+    </row>
+    <row r="163" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC163" s="2"/>
+      <c r="AD163" s="2"/>
+      <c r="AE163" s="2"/>
+      <c r="AF163" s="2"/>
+      <c r="AG163" s="2"/>
+    </row>
+    <row r="164" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC164" s="2"/>
+      <c r="AD164" s="2"/>
+      <c r="AE164" s="2"/>
+      <c r="AF164" s="2"/>
+      <c r="AG164" s="2"/>
+    </row>
+    <row r="165" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC165" s="2"/>
+      <c r="AD165" s="2"/>
+      <c r="AE165" s="2"/>
+      <c r="AF165" s="2"/>
+      <c r="AG165" s="2"/>
+    </row>
+    <row r="166" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC166" s="2"/>
+      <c r="AD166" s="2"/>
+      <c r="AE166" s="2"/>
+      <c r="AF166" s="2"/>
+      <c r="AG166" s="2"/>
+    </row>
+    <row r="167" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC167" s="2"/>
+      <c r="AD167" s="2"/>
+      <c r="AE167" s="2"/>
+      <c r="AF167" s="2"/>
+      <c r="AG167" s="2"/>
+    </row>
+    <row r="168" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC168" s="2"/>
+      <c r="AD168" s="2"/>
+      <c r="AE168" s="2"/>
+      <c r="AF168" s="2"/>
+      <c r="AG168" s="2"/>
+    </row>
+    <row r="169" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC169" s="2"/>
+      <c r="AD169" s="2"/>
+      <c r="AE169" s="2"/>
+      <c r="AF169" s="2"/>
+      <c r="AG169" s="2"/>
+    </row>
+    <row r="170" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC170" s="2"/>
+      <c r="AD170" s="2"/>
+      <c r="AE170" s="2"/>
+      <c r="AF170" s="2"/>
+      <c r="AG170" s="2"/>
+    </row>
+    <row r="171" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC171" s="2"/>
+      <c r="AD171" s="2"/>
+      <c r="AE171" s="2"/>
+      <c r="AF171" s="2"/>
+      <c r="AG171" s="2"/>
+    </row>
+    <row r="172" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC172" s="2"/>
+      <c r="AD172" s="2"/>
+      <c r="AE172" s="2"/>
+      <c r="AF172" s="2"/>
+      <c r="AG172" s="2"/>
+    </row>
+    <row r="173" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC173" s="2"/>
+      <c r="AD173" s="2"/>
+      <c r="AE173" s="2"/>
+      <c r="AF173" s="2"/>
+      <c r="AG173" s="2"/>
+    </row>
+    <row r="174" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC174" s="2"/>
+      <c r="AD174" s="2"/>
+      <c r="AE174" s="2"/>
+      <c r="AF174" s="2"/>
+      <c r="AG174" s="2"/>
+    </row>
+    <row r="175" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC175" s="2"/>
+      <c r="AD175" s="2"/>
+      <c r="AE175" s="2"/>
+      <c r="AF175" s="2"/>
+      <c r="AG175" s="2"/>
+    </row>
+    <row r="176" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC176" s="2"/>
+      <c r="AD176" s="2"/>
+      <c r="AE176" s="2"/>
+      <c r="AF176" s="2"/>
+      <c r="AG176" s="2"/>
+    </row>
+    <row r="177" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC177" s="2"/>
+      <c r="AD177" s="2"/>
+      <c r="AE177" s="2"/>
+      <c r="AF177" s="2"/>
+      <c r="AG177" s="2"/>
+    </row>
+    <row r="178" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC178" s="2"/>
+      <c r="AD178" s="2"/>
+      <c r="AE178" s="2"/>
+      <c r="AF178" s="2"/>
+      <c r="AG178" s="2"/>
+    </row>
+    <row r="179" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC179" s="2"/>
+      <c r="AD179" s="2"/>
+      <c r="AE179" s="2"/>
+      <c r="AF179" s="2"/>
+      <c r="AG179" s="2"/>
+    </row>
+    <row r="180" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC180" s="2"/>
+      <c r="AD180" s="2"/>
+      <c r="AE180" s="2"/>
+      <c r="AF180" s="2"/>
+      <c r="AG180" s="2"/>
+    </row>
+    <row r="181" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC181" s="2"/>
+      <c r="AD181" s="2"/>
+      <c r="AE181" s="2"/>
+      <c r="AF181" s="2"/>
+      <c r="AG181" s="2"/>
+    </row>
+    <row r="182" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC182" s="2"/>
+      <c r="AD182" s="2"/>
+      <c r="AE182" s="2"/>
+      <c r="AF182" s="2"/>
+      <c r="AG182" s="2"/>
+    </row>
+    <row r="183" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC183" s="2"/>
+      <c r="AD183" s="2"/>
+      <c r="AE183" s="2"/>
+      <c r="AF183" s="2"/>
+      <c r="AG183" s="2"/>
+    </row>
+    <row r="184" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC184" s="2"/>
+      <c r="AD184" s="2"/>
+      <c r="AE184" s="2"/>
+      <c r="AF184" s="2"/>
+      <c r="AG184" s="2"/>
+    </row>
+    <row r="185" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC185" s="2"/>
+      <c r="AD185" s="2"/>
+      <c r="AE185" s="2"/>
+      <c r="AF185" s="2"/>
+      <c r="AG185" s="2"/>
+    </row>
+    <row r="186" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC186" s="2"/>
+      <c r="AD186" s="2"/>
+      <c r="AE186" s="2"/>
+      <c r="AF186" s="2"/>
+      <c r="AG186" s="2"/>
+    </row>
+    <row r="187" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC187" s="2"/>
+      <c r="AD187" s="2"/>
+      <c r="AE187" s="2"/>
+      <c r="AF187" s="2"/>
+      <c r="AG187" s="2"/>
+    </row>
+    <row r="188" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC188" s="2"/>
+      <c r="AD188" s="2"/>
+      <c r="AE188" s="2"/>
+      <c r="AF188" s="2"/>
+      <c r="AG188" s="2"/>
+    </row>
+    <row r="189" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC189" s="2"/>
+      <c r="AD189" s="2"/>
+      <c r="AE189" s="2"/>
+      <c r="AF189" s="2"/>
+      <c r="AG189" s="2"/>
+    </row>
+    <row r="190" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC190" s="2"/>
+      <c r="AD190" s="2"/>
+      <c r="AE190" s="2"/>
+      <c r="AF190" s="2"/>
+      <c r="AG190" s="2"/>
+    </row>
+    <row r="191" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC191" s="2"/>
+      <c r="AD191" s="2"/>
+      <c r="AE191" s="2"/>
+      <c r="AF191" s="2"/>
+      <c r="AG191" s="2"/>
+    </row>
+    <row r="192" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC192" s="2"/>
+      <c r="AD192" s="2"/>
+      <c r="AE192" s="2"/>
+      <c r="AF192" s="2"/>
+      <c r="AG192" s="2"/>
+    </row>
+    <row r="193" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC193" s="2"/>
+      <c r="AD193" s="2"/>
+      <c r="AE193" s="2"/>
+      <c r="AF193" s="2"/>
+      <c r="AG193" s="2"/>
+    </row>
+    <row r="194" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC194" s="2"/>
+      <c r="AD194" s="2"/>
+      <c r="AE194" s="2"/>
+      <c r="AF194" s="2"/>
+      <c r="AG194" s="2"/>
+    </row>
+    <row r="195" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC195" s="2"/>
+      <c r="AD195" s="2"/>
+      <c r="AE195" s="2"/>
+      <c r="AF195" s="2"/>
+      <c r="AG195" s="2"/>
+    </row>
+    <row r="196" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC196" s="2"/>
+      <c r="AD196" s="2"/>
+      <c r="AE196" s="2"/>
+      <c r="AF196" s="2"/>
+      <c r="AG196" s="2"/>
+    </row>
+    <row r="197" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC197" s="2"/>
+      <c r="AD197" s="2"/>
+      <c r="AE197" s="2"/>
+      <c r="AF197" s="2"/>
+      <c r="AG197" s="2"/>
+    </row>
+    <row r="198" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC198" s="2"/>
+      <c r="AD198" s="2"/>
+      <c r="AE198" s="2"/>
+      <c r="AF198" s="2"/>
+      <c r="AG198" s="2"/>
+    </row>
+    <row r="199" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC199" s="2"/>
+      <c r="AD199" s="2"/>
+      <c r="AE199" s="2"/>
+      <c r="AF199" s="2"/>
+      <c r="AG199" s="2"/>
+    </row>
+    <row r="200" spans="29:33" x14ac:dyDescent="0.25">
+      <c r="AC200" s="5"/>
+      <c r="AD200" s="5"/>
+      <c r="AE200" s="5"/>
+      <c r="AF200" s="46">
         <f ca="1">TODAY()</f>
-        <v>46266</v>
-      </c>
-      <c r="AG36" s="4" cm="1">
-        <f t="array" ref="AG36">LOOKUP(2,1/(H:H&gt;0),H:H)</f>
-        <v>860.34665192519992</v>
+        <v>46296</v>
+      </c>
+      <c r="AG200" s="4" cm="1">
+        <f t="array" ref="AG200">LOOKUP(2,1/(H:H&gt;0),H:H)</f>
+        <v>974.40370280651996</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AE3:AE4"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="AF3:AG3"/>
+    <mergeCell ref="Y3:Y4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="V3:W3"/>
     <mergeCell ref="O3:O4"/>
     <mergeCell ref="P3:P4"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:U3"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AE3:AE4"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="AF3:AG3"/>
-    <mergeCell ref="Y3:Y4"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" location="'2026.01'!A1" display="'2026.01'!A1" xr:uid="{BAF6215B-37D5-4AB2-9B9C-F1057A1F97E5}"/>
@@ -9646,11 +11292,12 @@
     <hyperlink ref="A10" location="'2026.06'!A1" display="'2026.06'!A1" xr:uid="{F3608F29-46AC-4471-94DD-E0C306FF3FA3}"/>
     <hyperlink ref="A11" location="'2026.07'!A1" display="'2026.07'!A1" xr:uid="{D0DD87A1-01F2-4AC6-948E-9098F2EEF6C1}"/>
     <hyperlink ref="A12" location="'2026.08'!A1" display="'2026.08'!A1" xr:uid="{08493110-847F-414B-BF99-AD3F9DD09E97}"/>
+    <hyperlink ref="A13" location="'2026.09'!A1" display="'2026.09'!A1" xr:uid="{24B4C2ED-990E-4DD1-9E08-53E92C7856AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="E5:E12" formula="1"/>
+    <ignoredError sqref="E5:E13" formula="1"/>
   </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
